--- a/results/technical_validation/df_validation_nrcan_usgs.xlsx
+++ b/results/technical_validation/df_validation_nrcan_usgs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/results/technical_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_6831F2E19251260E62355476585DCE3A8747849C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{250150D9-2B03-4674-A522-0586B340FAAA}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="11_6831F2E19251260E62355476585DCE3A8747849C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F017318-BF28-4442-8299-C5DC2E4A551A}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="89">
   <si>
     <t>Commodity</t>
   </si>
@@ -65,9 +65,6 @@
     <t>16100019</t>
   </si>
   <si>
-    <t>3258153.0</t>
-  </si>
-  <si>
     <t>Smelter production, aluminum</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>alloys</t>
   </si>
   <si>
-    <t>43691.0</t>
-  </si>
-  <si>
     <t>bauxite</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
     <t>Kilograms</t>
   </si>
   <si>
-    <t>4923.174</t>
-  </si>
-  <si>
     <t>Mine production, cobalt content, estimated</t>
   </si>
   <si>
@@ -122,18 +113,12 @@
     <t>16100022</t>
   </si>
   <si>
-    <t>3260.0</t>
-  </si>
-  <si>
     <t>copper</t>
   </si>
   <si>
     <t>Mine production, recoverable copper content</t>
   </si>
   <si>
-    <t>484552.0</t>
-  </si>
-  <si>
     <t>concentrates</t>
   </si>
   <si>
@@ -149,9 +134,6 @@
     <t>Carats</t>
   </si>
   <si>
-    <t>3.1348702</t>
-  </si>
-  <si>
     <t>gemstones</t>
   </si>
   <si>
@@ -164,9 +146,6 @@
     <t>gold</t>
   </si>
   <si>
-    <t>191.035</t>
-  </si>
-  <si>
     <t>mine production, gold content</t>
   </si>
   <si>
@@ -176,9 +155,6 @@
     <t>crude and dore</t>
   </si>
   <si>
-    <t>215.873</t>
-  </si>
-  <si>
     <t>graphite</t>
   </si>
   <si>
@@ -197,21 +173,12 @@
     <t>Grams</t>
   </si>
   <si>
-    <t>0.09189499999999999</t>
-  </si>
-  <si>
     <t>iron</t>
   </si>
   <si>
-    <t>65165564.0</t>
-  </si>
-  <si>
     <t>agglomerates</t>
   </si>
   <si>
-    <t>17708017.0</t>
-  </si>
-  <si>
     <t>iron and steel</t>
   </si>
   <si>
@@ -239,9 +206,6 @@
     <t>Mine production, lithium content</t>
   </si>
   <si>
-    <t>31600.0</t>
-  </si>
-  <si>
     <t>magnesium compounds</t>
   </si>
   <si>
@@ -254,24 +218,12 @@
     <t>Mine production, molybdenum content</t>
   </si>
   <si>
-    <t>2537.0</t>
-  </si>
-  <si>
-    <t>1171.0</t>
-  </si>
-  <si>
     <t>nickel</t>
   </si>
   <si>
     <t>Mine production, nickel content</t>
   </si>
   <si>
-    <t>127237.0</t>
-  </si>
-  <si>
-    <t>949184.0</t>
-  </si>
-  <si>
     <t>niobium</t>
   </si>
   <si>
@@ -281,27 +233,12 @@
     <t>palladium</t>
   </si>
   <si>
-    <t>39792.0</t>
-  </si>
-  <si>
-    <t>17.267477</t>
-  </si>
-  <si>
     <t>platinum</t>
   </si>
   <si>
-    <t>6.1197799999999996</t>
-  </si>
-  <si>
     <t>platinum group</t>
   </si>
   <si>
-    <t>23.970214</t>
-  </si>
-  <si>
-    <t>11.541177</t>
-  </si>
-  <si>
     <t>platinum-group metals</t>
   </si>
   <si>
@@ -317,15 +254,9 @@
     <t>rhodium</t>
   </si>
   <si>
-    <t>0.33366799999999996</t>
-  </si>
-  <si>
     <t>ruthenium</t>
   </si>
   <si>
-    <t>0.157394</t>
-  </si>
-  <si>
     <t>selenium</t>
   </si>
   <si>
@@ -344,12 +275,6 @@
     <t>silver</t>
   </si>
   <si>
-    <t>240.523</t>
-  </si>
-  <si>
-    <t>6720.981</t>
-  </si>
-  <si>
     <t>Mine production, silver content</t>
   </si>
   <si>
@@ -368,28 +293,13 @@
     <t>uranium</t>
   </si>
   <si>
-    <t>12366.0</t>
-  </si>
-  <si>
-    <t>13884.0</t>
-  </si>
-  <si>
     <t>wollastonite</t>
   </si>
   <si>
     <t>zeolite</t>
   </si>
   <si>
-    <t>565.0</t>
-  </si>
-  <si>
     <t>zinc</t>
-  </si>
-  <si>
-    <t>109507.0</t>
-  </si>
-  <si>
-    <t>177439.0</t>
   </si>
 </sst>
 </file>
@@ -408,9 +318,10 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,17 +330,183 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -442,134 +519,61 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -886,456 +890,456 @@
     <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="12">
         <v>3258153</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="13">
+        <v>3258153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
       </c>
       <c r="D3">
         <v>3200</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="11">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="17">
         <v>43691</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>15</v>
+      <c r="F4" s="18">
+        <v>43691</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
       </c>
       <c r="D5">
         <v>1500</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2">
         <v>1500000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
       </c>
       <c r="D6">
         <v>1800</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2">
         <v>1800</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="4">
+        <v>4923174</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="8">
+        <v>4923.174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4923174</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>4220</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="11">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9">
         <v>4220</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>3260</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="9">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="12">
+        <v>500</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="13">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="8">
-        <v>3260</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D11">
+        <v>484552</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="15">
+        <v>484552</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>1272135</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="15">
+        <v>1272135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="14">
-        <v>500</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="15">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="17">
-        <v>484552</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="17">
-        <v>1272135</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="18">
-        <v>1272135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="20">
+      <c r="C13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="17">
         <v>315</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="21">
+      <c r="E13" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="18">
         <v>315000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>15674351</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3.1348701999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>16000</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="3">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2">
         <v>3.2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="A16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="5">
+      <c r="C16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="12">
         <v>191035</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>43</v>
+      <c r="E16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="13">
+        <v>191.035</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>42</v>
+      <c r="A17" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17">
         <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="11">
+        <v>12</v>
+      </c>
+      <c r="F17" s="15">
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="8">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="17">
         <v>215873</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>47</v>
+      <c r="E18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="18">
+        <v>215.87299999999999</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>5470</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="3">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2">
         <v>5470</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="3">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>91895</v>
       </c>
       <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9.1894999999999893E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="12">
         <v>65165564</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>56</v>
+      <c r="E22" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="13">
+        <v>65165564</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>55</v>
+      <c r="A23" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
@@ -1344,178 +1348,178 @@
         <v>17708017</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>58</v>
+        <v>25</v>
+      </c>
+      <c r="F23" s="15">
+        <v>17708017</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>59</v>
+      <c r="A24" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D24">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="11">
+        <v>12</v>
+      </c>
+      <c r="F24" s="15">
         <v>12000000</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>59</v>
+      <c r="A25" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="11">
+        <v>12</v>
+      </c>
+      <c r="F25" s="15">
         <v>6000000</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>63</v>
+      <c r="A26" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26">
         <v>35700</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="11">
+        <v>12</v>
+      </c>
+      <c r="F26" s="15">
         <v>35700000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="8">
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="17">
         <v>59400</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="12">
+      <c r="E27" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="18">
         <v>59400000</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="A28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28">
         <v>3240</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="10">
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="21">
         <v>3240</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="A29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="8">
+      <c r="C29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="7">
         <v>31600000</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="22">
+        <v>31600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="23">
+        <v>150</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="24">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1150</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="8">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
         <v>28</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30">
-        <v>150</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="3">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1150</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="10">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
       </c>
       <c r="C32" t="s">
         <v>8</v>
@@ -1524,58 +1528,58 @@
         <v>2537</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>73</v>
+        <v>25</v>
+      </c>
+      <c r="F32" s="9">
+        <v>2537</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="A33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>1171</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>74</v>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="10">
+        <v>1171</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="A34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="4">
         <v>159000</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="10">
+      <c r="E34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="8">
         <v>159000</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>75</v>
+      <c r="A35" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
@@ -1584,141 +1588,141 @@
         <v>127237</v>
       </c>
       <c r="E35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="9">
+        <v>127237</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="7">
         <v>949184</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>78</v>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="10">
+        <v>949184</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D37">
         <v>6700</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2">
         <v>6700</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="A38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="4">
+        <v>39792000</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="8">
+        <v>39792</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="5">
-        <v>39792000</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" t="s">
-        <v>27</v>
-      </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D39">
         <v>17267477</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>83</v>
+        <v>25</v>
+      </c>
+      <c r="F39" s="9">
+        <v>17.267477</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>84</v>
+      <c r="A40" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D40">
         <v>6119780</v>
       </c>
       <c r="E40" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>85</v>
+        <v>25</v>
+      </c>
+      <c r="F40" s="9">
+        <v>6.1197799999999898</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>86</v>
+      <c r="A41" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D41">
         <v>23970214</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>87</v>
+        <v>25</v>
+      </c>
+      <c r="F41" s="9">
+        <v>23.970213999999999</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>86</v>
+      <c r="A42" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D42">
         <v>11541177</v>
@@ -1726,179 +1730,179 @@
       <c r="E42" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>88</v>
+      <c r="F42" s="9">
+        <v>11.541176999999999</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>89</v>
+      <c r="A43" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D43">
         <v>5170</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="11">
+        <v>12</v>
+      </c>
+      <c r="F43" s="9">
         <v>5.17</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="8">
+      <c r="A44" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="7">
         <v>16100</v>
       </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="12">
+      <c r="E44" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="10">
         <v>16.100000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D45">
         <v>333668</v>
       </c>
       <c r="E45" t="s">
-        <v>28</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>94</v>
+        <v>25</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.33366799999999902</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D46">
         <v>157394</v>
       </c>
       <c r="E46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>97</v>
-      </c>
-      <c r="B47" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47">
+        <v>25</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.15739400000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="23">
         <v>130</v>
       </c>
-      <c r="E47" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="E47" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="24">
         <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D48">
         <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="3">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2">
         <v>29000</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49">
         <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="3">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2">
         <v>23000</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="A50" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D50" s="5">
+      <c r="C50" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="12">
         <v>240523</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>103</v>
+      <c r="E50" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="13">
+        <v>240.523</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>102</v>
+      <c r="A51" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D51">
         <v>6720981</v>
@@ -1906,76 +1910,76 @@
       <c r="E51" t="s">
         <v>9</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="8">
+      <c r="F51" s="15">
+        <v>6720.9809999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="17">
         <v>306</v>
       </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="12">
+      <c r="E52" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="18">
         <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D53">
         <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="3">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2">
         <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <v>350</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="3">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2">
         <v>350</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
@@ -1984,18 +1988,18 @@
         <v>12366</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>111</v>
+        <v>25</v>
+      </c>
+      <c r="F55" s="2">
+        <v>12366</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
@@ -2004,58 +2008,58 @@
         <v>13884</v>
       </c>
       <c r="E56" t="s">
-        <v>28</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" t="s">
-        <v>49</v>
-      </c>
-      <c r="C57" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57">
+        <v>25</v>
+      </c>
+      <c r="F56" s="2">
+        <v>13884</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="23">
         <v>20000</v>
       </c>
-      <c r="E57" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="E57" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="24">
         <v>20000</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" t="s">
-        <v>36</v>
-      </c>
-      <c r="C58" t="s">
+    <row r="58" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="23">
         <v>565</v>
       </c>
-      <c r="E58" t="s">
-        <v>28</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>115</v>
+      <c r="E58" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="24">
+        <v>565</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
@@ -2064,18 +2068,18 @@
         <v>109507</v>
       </c>
       <c r="E59" t="s">
-        <v>28</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>117</v>
+        <v>25</v>
+      </c>
+      <c r="F59" s="2">
+        <v>109507</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
@@ -2084,10 +2088,10 @@
         <v>177439</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>118</v>
+        <v>25</v>
+      </c>
+      <c r="F60" s="2">
+        <v>177439</v>
       </c>
     </row>
   </sheetData>
